--- a/AAII_Financials/Quarterly/PFTA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PFTA_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="92">
   <si>
     <t>PFTA</t>
   </si>
@@ -656,71 +656,72 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
@@ -730,8 +731,11 @@
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -777,8 +781,11 @@
       <c r="Q8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -824,8 +831,11 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -871,8 +881,11 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -890,8 +903,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -937,8 +951,11 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -984,31 +1001,34 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>-1300</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1031,8 +1051,11 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1078,8 +1101,11 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1094,43 +1120,44 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E17" s="3">
         <v>900</v>
-      </c>
-      <c r="E17" s="3">
-        <v>600</v>
       </c>
       <c r="F17" s="3">
         <v>600</v>
       </c>
       <c r="G17" s="3">
+        <v>600</v>
+      </c>
+      <c r="H17" s="3">
         <v>800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>200</v>
       </c>
-      <c r="M17" s="3">
-        <v>0</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
+      <c r="N17" s="3">
+        <v>0</v>
       </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
@@ -1141,8 +1168,11 @@
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1150,34 +1180,34 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
-        <v>-600</v>
+        <v>-900</v>
       </c>
       <c r="F18" s="3">
         <v>-600</v>
       </c>
       <c r="G18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="H18" s="3">
         <v>-800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-200</v>
       </c>
-      <c r="M18" s="3">
-        <v>0</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
+      <c r="N18" s="3">
+        <v>0</v>
       </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
@@ -1188,8 +1218,11 @@
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1207,8 +1240,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1216,34 +1250,34 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F20" s="3">
         <v>3800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>4500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>4000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>6500</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
+      <c r="N20" s="3">
+        <v>0</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
@@ -1254,8 +1288,11 @@
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1263,23 +1300,23 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F21" s="3">
         <v>3200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2100</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1301,8 +1338,11 @@
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1348,43 +1388,46 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E23" s="3">
         <v>4000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-200</v>
       </c>
-      <c r="M23" s="3">
-        <v>0</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
+      <c r="N23" s="3">
+        <v>0</v>
       </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
@@ -1395,8 +1438,11 @@
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1442,8 +1488,11 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1489,43 +1538,46 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E26" s="3">
         <v>4000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-200</v>
       </c>
-      <c r="M26" s="3">
-        <v>0</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
+      <c r="N26" s="3">
+        <v>0</v>
       </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
@@ -1536,43 +1588,46 @@
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E27" s="3">
         <v>4000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-200</v>
       </c>
-      <c r="M27" s="3">
-        <v>0</v>
-      </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
+      <c r="N27" s="3">
+        <v>0</v>
       </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
@@ -1583,8 +1638,11 @@
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1630,8 +1688,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1677,8 +1738,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1724,8 +1788,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1771,8 +1838,11 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1780,34 +1850,34 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="F32" s="3">
         <v>-3800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-4500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-4000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-6500</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
+      <c r="N32" s="3">
+        <v>0</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
@@ -1818,43 +1888,46 @@
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E33" s="3">
         <v>4000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-200</v>
       </c>
-      <c r="M33" s="3">
-        <v>0</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
+      <c r="N33" s="3">
+        <v>0</v>
       </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
@@ -1865,8 +1938,11 @@
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1912,43 +1988,46 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E35" s="3">
         <v>4000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-200</v>
       </c>
-      <c r="M35" s="3">
-        <v>0</v>
-      </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
+      <c r="N35" s="3">
+        <v>0</v>
       </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
@@ -1959,49 +2038,52 @@
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2011,8 +2093,11 @@
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2030,8 +2115,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2049,38 +2135,39 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>100</v>
+      </c>
+      <c r="E41" s="3">
         <v>400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>300</v>
-      </c>
-      <c r="F41" s="3">
-        <v>400</v>
       </c>
       <c r="G41" s="3">
         <v>400</v>
       </c>
       <c r="H41" s="3">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="I41" s="3">
         <v>700</v>
       </c>
       <c r="J41" s="3">
+        <v>700</v>
+      </c>
+      <c r="K41" s="3">
         <v>1200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1600</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2096,8 +2183,11 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2143,8 +2233,11 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2190,8 +2283,11 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2237,38 +2333,41 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>400</v>
+      </c>
+      <c r="E45" s="3">
         <v>100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>700</v>
-      </c>
-      <c r="H45" s="3">
-        <v>900</v>
       </c>
       <c r="I45" s="3">
         <v>900</v>
       </c>
       <c r="J45" s="3">
+        <v>900</v>
+      </c>
+      <c r="K45" s="3">
         <v>800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>900</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2284,8 +2383,11 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2293,29 +2395,29 @@
         <v>500</v>
       </c>
       <c r="E46" s="3">
+        <v>500</v>
+      </c>
+      <c r="F46" s="3">
         <v>600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2400</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2331,37 +2433,40 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>41200</v>
+      </c>
+      <c r="E47" s="3">
         <v>269200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>266000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>263300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>261100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>259700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>259200</v>
-      </c>
-      <c r="J47" s="3">
-        <v>259100</v>
       </c>
       <c r="K47" s="3">
         <v>259100</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
+      <c r="L47" s="3">
+        <v>259100</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
@@ -2378,8 +2483,11 @@
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2425,8 +2533,11 @@
       <c r="Q48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2472,8 +2583,11 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2519,8 +2633,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2566,8 +2683,11 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2577,33 +2697,33 @@
       <c r="E52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F52" s="3">
-        <v>0</v>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G52" s="3">
         <v>0</v>
       </c>
       <c r="H52" s="3">
+        <v>0</v>
+      </c>
+      <c r="I52" s="3">
         <v>100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>200</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2613,8 +2733,11 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2660,44 +2783,47 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>41800</v>
+      </c>
+      <c r="E54" s="3">
         <v>269700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>266600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>264100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>262300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>261300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>261100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>261600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>262200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>200</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2707,8 +2833,11 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2726,8 +2855,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2745,8 +2875,9 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2765,12 +2896,12 @@
       <c r="H57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I57" s="3">
+      <c r="I57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J57" s="3">
         <v>900</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2783,8 +2914,8 @@
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
+      <c r="O57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P57" s="3">
         <v>0</v>
@@ -2792,17 +2923,20 @@
       <c r="Q57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E58" s="3">
         <v>1300</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2815,21 +2949,21 @@
       <c r="I58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3">
+      <c r="J58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M58" s="3">
         <v>600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>100</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2839,44 +2973,47 @@
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>300</v>
+      </c>
+      <c r="E59" s="3">
         <v>1800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1200</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K59" s="3">
         <v>800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>100</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2886,44 +3023,47 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>300</v>
+      </c>
+      <c r="E60" s="3">
         <v>3000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>200</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2933,8 +3073,11 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2980,38 +3123,41 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E62" s="3">
         <v>600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>12100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>16200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>19000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>22900</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3027,8 +3173,11 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3074,8 +3223,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3121,8 +3273,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3168,44 +3323,47 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E66" s="3">
         <v>3600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>13300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>17100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>19700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>23000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>200</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3215,8 +3373,11 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3234,8 +3395,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3281,8 +3443,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3328,8 +3493,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3375,8 +3543,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3422,43 +3593,46 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-11600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-11500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-12300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-12800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-11900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-11700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-15100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-17200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-19900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-200</v>
       </c>
-      <c r="M72" s="3">
-        <v>0</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
+      <c r="N72" s="3">
+        <v>0</v>
       </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
@@ -3469,8 +3643,11 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3516,8 +3693,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3563,8 +3743,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3610,43 +3793,46 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>39600</v>
+      </c>
+      <c r="E76" s="3">
         <v>266100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>259900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>256700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>255500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>247900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>244000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>241900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>239300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-100</v>
       </c>
-      <c r="M76" s="3">
-        <v>0</v>
-      </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
+      <c r="N76" s="3">
+        <v>0</v>
       </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
@@ -3657,8 +3843,11 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3704,49 +3893,52 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3756,43 +3948,46 @@
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E81" s="3">
         <v>4000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-200</v>
       </c>
-      <c r="M81" s="3">
-        <v>0</v>
-      </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
+      <c r="N81" s="3">
+        <v>0</v>
       </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
@@ -3803,8 +3998,11 @@
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3822,8 +4020,9 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3869,8 +4068,11 @@
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3916,8 +4118,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3963,8 +4168,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4010,8 +4218,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4057,8 +4268,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4104,43 +4318,46 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-100</v>
       </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
       <c r="G89" s="3">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3">
         <v>-300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2600</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
       <c r="M89" s="3">
         <v>0</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
+      <c r="N89" s="3">
+        <v>0</v>
       </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
@@ -4151,8 +4368,11 @@
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4170,8 +4390,9 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4217,8 +4438,11 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4264,8 +4488,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4311,8 +4538,11 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4358,8 +4588,11 @@
       <c r="Q94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4377,8 +4610,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4424,8 +4658,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4471,8 +4708,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4518,8 +4758,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4565,22 +4808,25 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
+      <c r="D100" s="3">
+        <v>-228600</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
+      <c r="F100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="3">
+        <v>0</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>3</v>
@@ -4588,12 +4834,12 @@
       <c r="I100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K100" s="3">
         <v>-800</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4612,8 +4858,11 @@
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4659,43 +4908,46 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E102" s="3">
         <v>200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-100</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-100</v>
-      </c>
-      <c r="I102" s="3">
-        <v>-400</v>
       </c>
       <c r="J102" s="3">
         <v>-400</v>
       </c>
       <c r="K102" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L102" s="3">
         <v>1600</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
         <v>0</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
+      <c r="N102" s="3">
+        <v>0</v>
       </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
@@ -4704,6 +4956,9 @@
         <v>3</v>
       </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PFTA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PFTA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="92">
   <si>
     <t>PFTA</t>
   </si>
@@ -656,86 +656,93 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -784,8 +791,14 @@
       <c r="R8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -834,8 +847,14 @@
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -884,8 +903,14 @@
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -904,8 +929,10 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -954,8 +981,14 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1004,20 +1037,26 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>-1300</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1030,11 +1069,11 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1054,8 +1093,14 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1104,8 +1149,14 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1121,49 +1172,51 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F17" s="3">
         <v>-700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>600</v>
-      </c>
-      <c r="G17" s="3">
-        <v>600</v>
-      </c>
-      <c r="H17" s="3">
-        <v>800</v>
       </c>
       <c r="I17" s="3">
         <v>600</v>
       </c>
       <c r="J17" s="3">
+        <v>800</v>
+      </c>
+      <c r="K17" s="3">
+        <v>600</v>
+      </c>
+      <c r="L17" s="3">
         <v>700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>200</v>
       </c>
-      <c r="N17" s="3">
-        <v>0</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
+      <c r="P17" s="3">
+        <v>0</v>
       </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
@@ -1171,8 +1224,14 @@
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1180,40 +1239,40 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F18" s="3">
+        <v>700</v>
+      </c>
+      <c r="G18" s="3">
         <v>-900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-600</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-600</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-800</v>
       </c>
       <c r="I18" s="3">
         <v>-600</v>
       </c>
       <c r="J18" s="3">
+        <v>-800</v>
+      </c>
+      <c r="K18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="L18" s="3">
         <v>-700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-1300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-1100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-200</v>
       </c>
-      <c r="N18" s="3">
-        <v>0</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
+      <c r="P18" s="3">
+        <v>0</v>
       </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
@@ -1221,8 +1280,14 @@
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1241,8 +1306,10 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1250,40 +1317,40 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>400</v>
+      </c>
+      <c r="G20" s="3">
         <v>4900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>3800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>1800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>2100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>4500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>2800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>4000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>6500</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
@@ -1291,8 +1358,14 @@
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1300,29 +1373,29 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G21" s="3">
         <v>4000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>3200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>1200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>1300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>3900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>2100</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1341,8 +1414,14 @@
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1391,49 +1470,55 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>600</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F23" s="3">
         <v>1100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>4000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>3200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>1200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>1300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>3900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>2100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>2600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>5400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-200</v>
       </c>
-      <c r="N23" s="3">
-        <v>0</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
+      <c r="P23" s="3">
+        <v>0</v>
       </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
@@ -1441,8 +1526,14 @@
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1491,8 +1582,14 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1541,49 +1638,55 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F26" s="3">
         <v>1100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>4000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>3200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>1200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>1300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>3900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>2100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>2600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>5400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-200</v>
       </c>
-      <c r="N26" s="3">
-        <v>0</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
+      <c r="P26" s="3">
+        <v>0</v>
       </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
@@ -1591,49 +1694,55 @@
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F27" s="3">
         <v>1100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>4000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>3200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>1200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>1300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>3900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>2100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>2600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>5400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-200</v>
       </c>
-      <c r="N27" s="3">
-        <v>0</v>
-      </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
+      <c r="P27" s="3">
+        <v>0</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
@@ -1641,8 +1750,14 @@
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1691,8 +1806,14 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1741,8 +1862,14 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1791,8 +1918,14 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1841,8 +1974,14 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1850,40 +1989,40 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G32" s="3">
         <v>-4900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-3800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-1800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-2100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-4500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-2800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-4000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-6500</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
@@ -1891,49 +2030,55 @@
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F33" s="3">
         <v>1100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>4000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>3200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>1200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>1300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>3900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>2100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>2600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>5400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-200</v>
       </c>
-      <c r="N33" s="3">
-        <v>0</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
+      <c r="P33" s="3">
+        <v>0</v>
       </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
@@ -1941,8 +2086,14 @@
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1991,49 +2142,55 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F35" s="3">
         <v>1100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>4000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>3200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>1200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>1300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>3900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>2100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>2600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>5400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-200</v>
       </c>
-      <c r="N35" s="3">
-        <v>0</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
+      <c r="P35" s="3">
+        <v>0</v>
       </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
@@ -2041,63 +2198,75 @@
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2116,8 +2285,10 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2136,44 +2307,46 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>300</v>
+      </c>
+      <c r="E41" s="3">
         <v>100</v>
       </c>
-      <c r="E41" s="3">
-        <v>400</v>
-      </c>
       <c r="F41" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="G41" s="3">
         <v>400</v>
       </c>
       <c r="H41" s="3">
+        <v>300</v>
+      </c>
+      <c r="I41" s="3">
         <v>400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
+        <v>400</v>
+      </c>
+      <c r="K41" s="3">
         <v>700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1600</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2186,8 +2359,14 @@
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2236,8 +2415,14 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2286,8 +2471,14 @@
       <c r="R43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2336,43 +2527,49 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>300</v>
+      </c>
+      <c r="F45" s="3">
         <v>400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>900</v>
-      </c>
-      <c r="J45" s="3">
-        <v>900</v>
-      </c>
-      <c r="K45" s="3">
-        <v>800</v>
       </c>
       <c r="L45" s="3">
         <v>900</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
+      <c r="M45" s="3">
+        <v>800</v>
+      </c>
+      <c r="N45" s="3">
+        <v>900</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
@@ -2386,8 +2583,14 @@
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2395,35 +2598,35 @@
         <v>500</v>
       </c>
       <c r="E46" s="3">
+        <v>400</v>
+      </c>
+      <c r="F46" s="3">
         <v>500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
+        <v>500</v>
+      </c>
+      <c r="H46" s="3">
         <v>600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>2000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>2400</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2436,44 +2639,50 @@
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>42100</v>
+      </c>
+      <c r="E47" s="3">
+        <v>41700</v>
+      </c>
+      <c r="F47" s="3">
         <v>41200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>269200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>266000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>263300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>261100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>259700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>259200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>259100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>259100</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2486,8 +2695,14 @@
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2536,8 +2751,14 @@
       <c r="R48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2586,8 +2807,14 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2636,8 +2863,14 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2686,8 +2919,14 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2700,44 +2939,50 @@
       <c r="F52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3">
         <v>100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>200</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2786,58 +3031,70 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>42600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>42100</v>
+      </c>
+      <c r="F54" s="3">
         <v>41800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>269700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>266600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>264100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>262300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>261300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>261100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>261600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>262200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>200</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2856,8 +3113,10 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2876,38 +3135,40 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
+      <c r="D57" s="3">
+        <v>0</v>
+      </c>
+      <c r="E57" s="3">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3">
+        <v>0</v>
+      </c>
+      <c r="G57" s="3">
+        <v>0</v>
+      </c>
+      <c r="H57" s="3">
+        <v>0</v>
+      </c>
+      <c r="I57" s="3">
+        <v>0</v>
       </c>
       <c r="J57" s="3">
+        <v>0</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L57" s="3">
         <v>900</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2917,32 +3178,38 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P57" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>0</v>
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3">
+        <v>0</v>
+      </c>
+      <c r="T57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E58" s="3">
+      <c r="E58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G58" s="3">
         <v>1300</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2952,73 +3219,79 @@
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
+      <c r="K58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3">
         <v>600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>100</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F59" s="3">
         <v>300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>2200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1200</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3">
         <v>800</v>
-      </c>
-      <c r="L59" s="3">
-        <v>100</v>
-      </c>
-      <c r="M59" s="3">
-        <v>400</v>
       </c>
       <c r="N59" s="3">
         <v>100</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
+      <c r="O59" s="3">
+        <v>400</v>
+      </c>
+      <c r="P59" s="3">
+        <v>100</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
@@ -3026,58 +3299,70 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F60" s="3">
         <v>300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>3000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>200</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3126,44 +3411,50 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E62" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F62" s="3">
         <v>1900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>4500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>5600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>5300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>12100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>16200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>19000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>22900</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3176,8 +3467,14 @@
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3226,8 +3523,14 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3276,8 +3579,14 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3326,58 +3635,70 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>3700</v>
+      </c>
+      <c r="F66" s="3">
         <v>2200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>3600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>6700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>7400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>6800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>13300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>17100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>19700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>23000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>200</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3396,8 +3717,10 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3446,8 +3769,14 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3496,8 +3825,14 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3546,8 +3881,14 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3596,49 +3937,55 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="F72" s="3">
         <v>-11600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-11500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-12300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-12800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-11900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-11700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-15100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-17200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-19900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-200</v>
       </c>
-      <c r="N72" s="3">
-        <v>0</v>
-      </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
+      <c r="P72" s="3">
+        <v>0</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
@@ -3646,8 +3993,14 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3696,8 +4049,14 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3746,8 +4105,14 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3796,49 +4161,55 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>38400</v>
+      </c>
+      <c r="F76" s="3">
         <v>39600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>266100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>259900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>256700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>255500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>247900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>244000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>241900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>239300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>-100</v>
       </c>
-      <c r="N76" s="3">
-        <v>0</v>
-      </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
+      <c r="P76" s="3">
+        <v>0</v>
       </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
@@ -3846,8 +4217,14 @@
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3896,104 +4273,116 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F81" s="3">
         <v>1100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>4000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>3200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>1200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>1300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>3900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>2100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>2600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>5400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-200</v>
       </c>
-      <c r="N81" s="3">
-        <v>0</v>
-      </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
+      <c r="P81" s="3">
+        <v>0</v>
       </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
@@ -4001,8 +4390,14 @@
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4021,8 +4416,10 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4071,8 +4468,14 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4121,8 +4524,14 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4171,8 +4580,14 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4221,8 +4636,14 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4271,8 +4692,14 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4321,49 +4748,55 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F89" s="3">
         <v>-900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-1100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-100</v>
       </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3">
         <v>-300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-2600</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
-      <c r="N89" s="3">
-        <v>0</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
+      <c r="O89" s="3">
+        <v>0</v>
+      </c>
+      <c r="P89" s="3">
+        <v>0</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
@@ -4371,8 +4804,14 @@
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4391,8 +4830,10 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4441,8 +4882,14 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4491,8 +4938,14 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4541,8 +4994,14 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4591,8 +5050,14 @@
       <c r="R94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4611,8 +5076,10 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4661,8 +5128,14 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4711,8 +5184,14 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4761,8 +5240,14 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4811,41 +5296,47 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>300</v>
+      </c>
+      <c r="E100" s="3">
+        <v>100</v>
+      </c>
+      <c r="F100" s="3">
         <v>-228600</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
+      <c r="I100" s="3">
+        <v>0</v>
       </c>
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3">
         <v>-800</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4861,8 +5352,14 @@
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4911,54 +5408,66 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-100</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>1600</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
+      <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
+        <v>0</v>
       </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PFTA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PFTA_QTR_FIN.xlsx
@@ -656,82 +656,83 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
@@ -741,8 +742,11 @@
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -797,8 +801,11 @@
       <c r="T8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -853,8 +860,11 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -909,8 +919,11 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -931,8 +944,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -987,8 +1001,11 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1043,23 +1060,26 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>-1300</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1075,8 +1095,8 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1099,8 +1119,11 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1155,8 +1178,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1174,52 +1200,53 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>600</v>
+      </c>
+      <c r="E17" s="3">
         <v>800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>-700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>900</v>
-      </c>
-      <c r="H17" s="3">
-        <v>600</v>
       </c>
       <c r="I17" s="3">
         <v>600</v>
       </c>
       <c r="J17" s="3">
+        <v>600</v>
+      </c>
+      <c r="K17" s="3">
         <v>800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>200</v>
       </c>
-      <c r="P17" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
+      <c r="Q17" s="3">
+        <v>0</v>
       </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
@@ -1230,8 +1257,11 @@
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1239,43 +1269,43 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-900</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-600</v>
       </c>
       <c r="I18" s="3">
         <v>-600</v>
       </c>
       <c r="J18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="K18" s="3">
         <v>-800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-200</v>
       </c>
-      <c r="P18" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
+      <c r="Q18" s="3">
+        <v>0</v>
       </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
@@ -1286,8 +1316,11 @@
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1308,8 +1341,9 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1317,43 +1351,43 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>4900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>4500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>4000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>6500</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
+      <c r="Q20" s="3">
+        <v>0</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
@@ -1364,8 +1398,11 @@
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1373,32 +1410,32 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>600</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>4000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2100</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1420,8 +1457,11 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1476,52 +1516,55 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>300</v>
+      </c>
+      <c r="E23" s="3">
         <v>600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-200</v>
       </c>
-      <c r="P23" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
+      <c r="Q23" s="3">
+        <v>0</v>
       </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
@@ -1532,8 +1575,11 @@
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1588,8 +1634,11 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1644,52 +1693,55 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>300</v>
+      </c>
+      <c r="E26" s="3">
         <v>600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-200</v>
       </c>
-      <c r="P26" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
+      <c r="Q26" s="3">
+        <v>0</v>
       </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
@@ -1700,52 +1752,55 @@
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>300</v>
+      </c>
+      <c r="E27" s="3">
         <v>600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-200</v>
       </c>
-      <c r="P27" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
+      <c r="Q27" s="3">
+        <v>0</v>
       </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
@@ -1756,8 +1811,11 @@
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1812,8 +1870,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1868,8 +1929,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1924,8 +1988,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1980,8 +2047,11 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1989,43 +2059,43 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-1400</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-4900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-4500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-4000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-6500</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
+      <c r="Q32" s="3">
+        <v>0</v>
       </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
@@ -2036,52 +2106,55 @@
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>300</v>
+      </c>
+      <c r="E33" s="3">
         <v>600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-200</v>
       </c>
-      <c r="P33" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
+      <c r="Q33" s="3">
+        <v>0</v>
       </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
@@ -2092,8 +2165,11 @@
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2148,52 +2224,55 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>300</v>
+      </c>
+      <c r="E35" s="3">
         <v>600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-200</v>
       </c>
-      <c r="P35" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
+      <c r="Q35" s="3">
+        <v>0</v>
       </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
@@ -2204,58 +2283,61 @@
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2265,8 +2347,11 @@
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2287,8 +2372,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2309,47 +2395,48 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>100</v>
+      </c>
+      <c r="E41" s="3">
         <v>300</v>
-      </c>
-      <c r="E41" s="3">
-        <v>100</v>
       </c>
       <c r="F41" s="3">
         <v>100</v>
       </c>
       <c r="G41" s="3">
+        <v>100</v>
+      </c>
+      <c r="H41" s="3">
         <v>400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>300</v>
-      </c>
-      <c r="I41" s="3">
-        <v>400</v>
       </c>
       <c r="J41" s="3">
         <v>400</v>
       </c>
       <c r="K41" s="3">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="L41" s="3">
         <v>700</v>
       </c>
       <c r="M41" s="3">
+        <v>700</v>
+      </c>
+      <c r="N41" s="3">
         <v>1200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1600</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2365,8 +2452,11 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2421,8 +2511,11 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2477,8 +2570,11 @@
       <c r="T43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2533,47 +2629,50 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>100</v>
+      </c>
+      <c r="E45" s="3">
         <v>200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>700</v>
-      </c>
-      <c r="K45" s="3">
-        <v>900</v>
       </c>
       <c r="L45" s="3">
         <v>900</v>
       </c>
       <c r="M45" s="3">
+        <v>900</v>
+      </c>
+      <c r="N45" s="3">
         <v>800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>900</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2589,47 +2688,50 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>200</v>
+      </c>
+      <c r="E46" s="3">
         <v>500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>400</v>
-      </c>
-      <c r="F46" s="3">
-        <v>500</v>
       </c>
       <c r="G46" s="3">
         <v>500</v>
       </c>
       <c r="H46" s="3">
+        <v>500</v>
+      </c>
+      <c r="I46" s="3">
         <v>600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2400</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2645,46 +2747,49 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>42600</v>
+      </c>
+      <c r="E47" s="3">
         <v>42100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>41700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>41200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>269200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>266000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>263300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>261100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>259700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>259200</v>
-      </c>
-      <c r="M47" s="3">
-        <v>259100</v>
       </c>
       <c r="N47" s="3">
         <v>259100</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
+      <c r="O47" s="3">
+        <v>259100</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
@@ -2701,8 +2806,11 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2757,8 +2865,11 @@
       <c r="T48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2813,8 +2924,11 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2869,8 +2983,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2925,25 +3042,28 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
+      <c r="D52" s="3">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3">
+        <v>0</v>
       </c>
       <c r="I52" s="3">
         <v>0</v>
@@ -2952,26 +3072,26 @@
         <v>0</v>
       </c>
       <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3">
         <v>100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>200</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2981,8 +3101,11 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3037,53 +3160,56 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>42800</v>
+      </c>
+      <c r="E54" s="3">
         <v>42600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>42100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>41800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>269700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>266600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>264100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>262300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>261300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>261100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>261600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>262200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>200</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3093,8 +3219,11 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3115,8 +3244,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3137,8 +3267,9 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3163,15 +3294,15 @@
       <c r="J57" s="3">
         <v>0</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L57" s="3">
+      <c r="K57" s="3">
+        <v>0</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3">
         <v>900</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3184,8 +3315,8 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R57" s="3">
-        <v>0</v>
+      <c r="R57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S57" s="3">
         <v>0</v>
@@ -3193,8 +3324,11 @@
       <c r="T57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3207,12 +3341,12 @@
       <c r="F58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G58" s="3">
+      <c r="G58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H58" s="3">
         <v>1300</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3225,21 +3359,21 @@
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O58" s="3">
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P58" s="3">
         <v>600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>100</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3249,53 +3383,56 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>26900</v>
+      </c>
+      <c r="E59" s="3">
         <v>1800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1200</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3">
         <v>800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>100</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3305,53 +3442,56 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>26900</v>
+      </c>
+      <c r="E60" s="3">
         <v>1800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>200</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3361,8 +3501,11 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3417,47 +3560,50 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E62" s="3">
         <v>1800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>12100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>16200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>19000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>22900</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3473,8 +3619,11 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3529,8 +3678,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3585,8 +3737,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3641,53 +3796,56 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>28400</v>
+      </c>
+      <c r="E66" s="3">
         <v>3600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>17100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>19700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>23000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>200</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3697,8 +3855,11 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3719,8 +3880,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3775,8 +3937,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3831,8 +3996,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3887,8 +4055,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3943,52 +4114,55 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-3100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-3300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-11600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-11500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-12300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-12800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-11900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-11700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-15100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-17200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-19900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-200</v>
       </c>
-      <c r="P72" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
+      <c r="Q72" s="3">
+        <v>0</v>
       </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
@@ -3999,8 +4173,11 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4055,8 +4232,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4111,8 +4291,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4167,52 +4350,55 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E76" s="3">
         <v>39000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>38400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>39600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>266100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>259900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>256700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>255500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>247900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>244000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>241900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>239300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-100</v>
       </c>
-      <c r="P76" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
+      <c r="Q76" s="3">
+        <v>0</v>
       </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
@@ -4223,8 +4409,11 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4279,58 +4468,61 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4340,52 +4532,55 @@
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>300</v>
+      </c>
+      <c r="E81" s="3">
         <v>600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-200</v>
       </c>
-      <c r="P81" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
+      <c r="Q81" s="3">
+        <v>0</v>
       </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
@@ -4396,8 +4591,11 @@
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4418,8 +4616,9 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4474,8 +4673,11 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4530,8 +4732,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4586,8 +4791,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4642,8 +4850,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4698,8 +4909,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4754,8 +4968,11 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4763,43 +4980,43 @@
         <v>-200</v>
       </c>
       <c r="E89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F89" s="3">
         <v>-100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-100</v>
       </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
       <c r="J89" s="3">
+        <v>0</v>
+      </c>
+      <c r="K89" s="3">
         <v>-300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2600</v>
       </c>
-      <c r="O89" s="3">
-        <v>0</v>
-      </c>
       <c r="P89" s="3">
         <v>0</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
+      <c r="Q89" s="3">
+        <v>0</v>
       </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
@@ -4810,8 +5027,11 @@
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4832,8 +5052,9 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4888,8 +5109,11 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4944,8 +5168,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5000,8 +5227,11 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5056,8 +5286,11 @@
       <c r="T94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5078,8 +5311,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5134,8 +5368,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5190,8 +5427,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5246,8 +5486,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5302,31 +5545,34 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>100</v>
+      </c>
+      <c r="E100" s="3">
         <v>300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-228600</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
@@ -5334,12 +5580,12 @@
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3">
         <v>-800</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5358,8 +5604,11 @@
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5414,52 +5663,55 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E102" s="3">
         <v>200</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-100</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-100</v>
-      </c>
-      <c r="L102" s="3">
-        <v>-400</v>
       </c>
       <c r="M102" s="3">
         <v>-400</v>
       </c>
       <c r="N102" s="3">
+        <v>-400</v>
+      </c>
+      <c r="O102" s="3">
         <v>1600</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
       <c r="P102" s="3">
         <v>0</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
+      <c r="Q102" s="3">
+        <v>0</v>
       </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
@@ -5468,6 +5720,9 @@
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
